--- a/analysis/tables/gpt-neo-1.3B.xlsx
+++ b/analysis/tables/gpt-neo-1.3B.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8276207383753993</v>
+        <v>0.6014044032194567</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1713241130382146</v>
+        <v>-0.08304456761150539</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.828x - 0.171</t>
+          <t>y = 0.601x - 0.083</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8095504252942273</v>
+        <v>0.8095504252942268</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07443543144589623</v>
+        <v>0.07443543144589622</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2070079990679305</v>
+        <v>0.1380844023870604</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6562966253371847</v>
+        <v>0.5183598356079513</v>
       </c>
       <c r="K3" t="n">
         <v>0.1225311277835489</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8649654155528481</v>
+        <v>0.6000756819701113</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03982173357265753</v>
+        <v>-0.07743394604061768</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.865x - 0.040</t>
+          <t>y = 0.600x - 0.077</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8591659210976874</v>
+        <v>0.8140975457396832</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07264987319929</v>
+        <v>0.07427179006172348</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04603852692446116</v>
+        <v>0.1290403000274797</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8251436819801906</v>
+        <v>0.5226417359294936</v>
       </c>
       <c r="K4" t="n">
         <v>0.1225311277835489</v>
